--- a/sheets/대금율보/검수/이별가.xlsx
+++ b/sheets/대금율보/검수/이별가.xlsx
@@ -3356,8 +3356,7 @@
         <is>
           <t xml:space="preserve">–
 –浹ʒ
-浹フ
-‹</t>
+浹フ</t>
         </is>
       </c>
       <c r="C5" s="25"/>
@@ -3377,8 +3376,7 @@
         <is>
           <t xml:space="preserve">–
 –浹ʒ
-浹フ
-‹</t>
+浹フ</t>
         </is>
       </c>
       <c r="G5" s="25"/>
@@ -3421,8 +3419,7 @@
         <is>
           <t xml:space="preserve">–
 –
-㳞浹潢
-‹</t>
+㳞浹潢</t>
         </is>
       </c>
       <c r="E6" s="27"/>
@@ -3442,8 +3439,7 @@
         <is>
           <t xml:space="preserve">–
 –И
-Z
-‹</t>
+Z</t>
         </is>
       </c>
       <c r="I6" s="26"/>
@@ -3451,8 +3447,7 @@
         <is>
           <t xml:space="preserve">–
 –И
-淋
-‹</t>
+淋</t>
         </is>
       </c>
       <c r="K6" s="26"/>
@@ -3512,8 +3507,7 @@
         <is>
           <t xml:space="preserve">–
 –И
-淋ʒ
-‹</t>
+淋ʒ</t>
         </is>
       </c>
       <c r="E8" s="25"/>
@@ -3527,8 +3521,7 @@
         <is>
           <t xml:space="preserve">–
 –И
-淋
-‹</t>
+淋</t>
         </is>
       </c>
       <c r="I8" s="25"/>
@@ -3567,8 +3560,7 @@
         <is>
           <t xml:space="preserve">–
 –И
-浹浹フ
-‹</t>
+浹浹フ</t>
         </is>
       </c>
       <c r="G9" s="25"/>
@@ -3680,8 +3672,7 @@
         <is>
           <t xml:space="preserve">–
 –浹ʒ
-浹フ
-‹</t>
+浹フ</t>
         </is>
       </c>
       <c r="K11" s="22"/>
@@ -3692,8 +3683,7 @@
         <is>
           <t xml:space="preserve">潢無林
 潢無
-–)
-‹</t>
+–)</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
@@ -3717,8 +3707,7 @@
         <is>
           <t xml:space="preserve">潢無林
 潢無
-–)
-‹</t>
+–)</t>
         </is>
       </c>
       <c r="G12" s="24" t="inlineStr">
@@ -3757,7 +3746,7 @@
       <c r="C13" s="25"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 –И
 浹ʒ</t>
         </is>
@@ -3775,7 +3764,7 @@
       </c>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 –И
 浹ʒ</t>
         </is>
@@ -3838,7 +3827,7 @@
       <c r="D15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無
-–‹
+–
 林</t>
         </is>
       </c>
@@ -3854,7 +3843,7 @@
       <c r="H15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無
-–‹
+–
 林</t>
         </is>
       </c>

--- a/sheets/대금율보/검수/이별가.xlsx
+++ b/sheets/대금율보/검수/이별가.xlsx
@@ -3209,22 +3209,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="18.03" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="18.03" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="18.03" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="18.03" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="18.03" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="95.24" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="106.52" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="K3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="106.52" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="K4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="106.52" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="K5" s="25"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="106.52" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="K6" s="26"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="106.52" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="K7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="106.52" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="K8" s="25"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="106.52" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="23" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="K9" s="24"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="106.52" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
       <c r="J10" s="21"/>
       <c r="K10" s="26"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="106.52" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="K11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="106.52" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="23" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="K12" s="25"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="106.52" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="K13" s="24"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="106.52" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="26"/>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="K14" s="26"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="106.52" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="K15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="106.52" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="25"/>
@@ -3870,7 +3870,7 @@
       <c r="J16" s="21"/>
       <c r="K16" s="25"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="106.52" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="25"/>
@@ -3895,7 +3895,7 @@
       <c r="J17" s="21"/>
       <c r="K17" s="25"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="106.52" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="26"/>
@@ -3926,6 +3926,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="77"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="42"/>
 </worksheet>
 </file>